--- a/SWASH.xlsx
+++ b/SWASH.xlsx
@@ -11,120 +11,66 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="20">
   <si>
     <t/>
   </si>
   <si>
-    <t>20116112</t>
-  </si>
-  <si>
-    <t>MAXICORN BBQ 140G</t>
+    <t>20046081</t>
+  </si>
+  <si>
+    <t>G/D 3IN1 MCCINO 10'S</t>
   </si>
   <si>
     <t>SWASH</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20036590</t>
+  </si>
+  <si>
+    <t>LUWAK WHT ORGL 9X20</t>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
-    <t>10002101</t>
-  </si>
-  <si>
-    <t>HAPPYTOS CHIP MRH140</t>
-  </si>
-  <si>
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>20092857</t>
-  </si>
-  <si>
-    <t>STT FRENCH FRIES 130</t>
+    <t>10038932</t>
+  </si>
+  <si>
+    <t>KPL API SPC MIX 10'S</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
+    <t>10008882</t>
+  </si>
+  <si>
+    <t>K/API KOPI SPCL 150G</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20136451</t>
+  </si>
+  <si>
+    <t>NSCAFE AMERICANO 10S</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20139291</t>
-  </si>
-  <si>
-    <t>FLOATY SNACK BWNG 60</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20092063</t>
-  </si>
-  <si>
-    <t>CHITATO SAPI PGG 115</t>
-  </si>
-  <si>
-    <t>20116675</t>
-  </si>
-  <si>
-    <t>CHTATO LITE NORI 115</t>
-  </si>
-  <si>
-    <t>10001094</t>
-  </si>
-  <si>
-    <t>CHITATO SAPI PGG 65G</t>
-  </si>
-  <si>
-    <t>20116670</t>
-  </si>
-  <si>
-    <t>CHTATO LITE NORI 65G</t>
-  </si>
-  <si>
-    <t>20046081</t>
-  </si>
-  <si>
-    <t>G/D 3IN1 MCCINO 10'S</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20036590</t>
-  </si>
-  <si>
-    <t>LUWAK WHT ORGL 9X20</t>
-  </si>
-  <si>
-    <t>10038932</t>
-  </si>
-  <si>
-    <t>KPL API SPC MIX 10'S</t>
-  </si>
-  <si>
-    <t>10008882</t>
-  </si>
-  <si>
-    <t>K/API KOPI SPCL 150G</t>
-  </si>
-  <si>
-    <t>20136451</t>
-  </si>
-  <si>
-    <t>NSCAFE AMERICANO 10S</t>
-  </si>
-  <si>
-    <t>5</t>
   </si>
 </sst>
 </file>
@@ -517,14 +463,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="7" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -561,18 +507,18 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
@@ -581,7 +527,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>9</v>
@@ -604,15 +550,15 @@
         <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -621,190 +567,30 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/SWASH.xlsx
+++ b/SWASH.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="19">
   <si>
     <t/>
   </si>
@@ -28,13 +28,13 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-4B)</t>
+    <t>RT,(E-1B)</t>
   </si>
   <si>
     <t>20036590</t>
   </si>
   <si>
-    <t>LUWAK WHT ORGL 9X20</t>
+    <t>LUWAK WHT ORG 9x20 G</t>
   </si>
   <si>
     <t>2</t>
@@ -46,7 +46,7 @@
     <t>10038932</t>
   </si>
   <si>
-    <t>KPL API SPC MIX 10'S</t>
+    <t>K/A SPC MIX 10x23 G</t>
   </si>
   <si>
     <t>3</t>
@@ -68,9 +68,6 @@
   </si>
   <si>
     <t>5</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
   </si>
 </sst>
 </file>
@@ -590,7 +587,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
